--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>16520.349609375</v>
       </c>
       <c r="G2" t="n">
-        <v>59115.6015625</v>
+        <v>58180.5</v>
       </c>
       <c r="H2" t="n">
         <v>21476.25</v>
@@ -10724,7 +10724,7 @@
         <v>1.71</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>0.12</v>
       </c>
       <c r="H2" t="n">
         <v>1.08</v>
@@ -20945,7 +20945,7 @@
         <v>-1.46</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="H2" t="n">
         <v>-1.7</v>
@@ -31109,31 +31109,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.71</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="8">
@@ -31215,12 +31215,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -36327,7 +36327,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>16300.849609375</v>
       </c>
       <c r="G2" t="n">
-        <v>57792.55078125</v>
+        <v>57393.3515625</v>
       </c>
       <c r="H2" t="n">
         <v>21181.80078125</v>
@@ -10829,7 +10829,7 @@
         <v>0.36</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.54</v>
+        <v>-1.23</v>
       </c>
       <c r="H2" t="n">
         <v>-0.3</v>
@@ -21155,7 +21155,7 @@
         <v>-0.86</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>-0.68</v>
@@ -31448,7 +31448,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.54</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="8">
@@ -31530,7 +31530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -36693,7 +36693,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>15523.7001953125</v>
       </c>
       <c r="G2" t="n">
-        <v>56253.75</v>
+        <v>54761.1015625</v>
       </c>
       <c r="H2" t="n">
         <v>20233</v>
@@ -11004,7 +11004,7 @@
         <v>-4.42</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.19</v>
+        <v>-5.76</v>
       </c>
       <c r="H2" t="n">
         <v>-4.77</v>
@@ -21505,7 +21505,7 @@
         <v>-2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-2.65</v>
       </c>
       <c r="H2" t="n">
         <v>-2.68</v>
@@ -31929,51 +31929,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3.19</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-3.3</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-4.42</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4.71</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-4.77</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="8">
@@ -32055,12 +32055,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Next 50</t>
         </is>
       </c>
     </row>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.06%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>15572.599609375</v>
       </c>
       <c r="G2" t="n">
-        <v>54492.30078125</v>
+        <v>54855.5</v>
       </c>
       <c r="H2" t="n">
         <v>20226.900390625</v>
@@ -11179,7 +11179,7 @@
         <v>-4.12</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.22</v>
+        <v>-5.6</v>
       </c>
       <c r="H2" t="n">
         <v>-4.8</v>
@@ -21855,7 +21855,7 @@
         <v>0.74</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H2" t="n">
         <v>0.59</v>
@@ -32498,7 +32498,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-6.22</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="8">
@@ -32580,12 +32580,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-5.35%</t>
+          <t>-5.29%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>15731.4501953125</v>
       </c>
       <c r="G2" t="n">
-        <v>54087</v>
+        <v>55331.05078125</v>
       </c>
       <c r="H2" t="n">
         <v>20397.75</v>
@@ -11284,7 +11284,7 @@
         <v>-3.14</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.92</v>
+        <v>-4.78</v>
       </c>
       <c r="H2" t="n">
         <v>-3.99</v>
@@ -22065,7 +22065,7 @@
         <v>2.07</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
         <v>2.34</v>
@@ -32809,21 +32809,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.79</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nifty 500</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.88</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="9">
@@ -32839,11 +32839,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 500</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-6.92</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="11">
@@ -32895,12 +32895,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>-4.66%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>15396.099609375</v>
       </c>
       <c r="G2" t="n">
-        <v>55331.05078125</v>
+        <v>54097.80078125</v>
       </c>
       <c r="H2" t="n">
         <v>19952.75</v>
@@ -11319,7 +11319,7 @@
         <v>-5.21</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.78</v>
+        <v>-6.9</v>
       </c>
       <c r="H2" t="n">
         <v>-6.09</v>
@@ -22135,7 +22135,7 @@
         <v>-2.13</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="H2" t="n">
         <v>-2.18</v>
@@ -32874,51 +32874,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-4.78</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-5</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5.21</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6.09</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-6.51</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="8">
@@ -33000,12 +33000,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty Midcap 50</t>
+          <t>Nifty 50, Nifty Midcap 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -38401,7 +38401,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-6.54%</t>
+          <t>-6.75%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>14983.349609375</v>
       </c>
       <c r="G2" t="n">
-        <v>54097.80078125</v>
+        <v>52650</v>
       </c>
       <c r="H2" t="n">
         <v>19430.900390625</v>
@@ -11354,7 +11354,7 @@
         <v>-7.75</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.9</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>-8.550000000000001</v>
@@ -22205,7 +22205,7 @@
         <v>-2.68</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-2.68</v>
       </c>
       <c r="H2" t="n">
         <v>-2.62</v>
@@ -32979,51 +32979,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-6.9</v>
+        <v>-7.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-7.21</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-7.75</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-8.6</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -33105,12 +33105,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -38523,7 +38523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-8.76%</t>
+          <t>-9.01%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>15270.5</v>
       </c>
       <c r="G2" t="n">
-        <v>53819.1484375</v>
+        <v>53677.05078125</v>
       </c>
       <c r="H2" t="n">
         <v>19805.5</v>
@@ -11424,7 +11424,7 @@
         <v>-5.98</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.38</v>
+        <v>-7.63</v>
       </c>
       <c r="H2" t="n">
         <v>-6.78</v>
@@ -22345,7 +22345,7 @@
         <v>-0.16</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="H2" t="n">
         <v>-0.32</v>
@@ -33233,7 +33233,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-7.38</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="8">
@@ -33320,7 +33320,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
     </row>
@@ -38767,7 +38767,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-7.16%</t>
+          <t>-7.19%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>16452.400390625</v>
       </c>
       <c r="G2" t="n">
-        <v>56978.75</v>
+        <v>57843.94921875</v>
       </c>
       <c r="H2" t="n">
         <v>21300.30078125</v>
@@ -11599,7 +11599,7 @@
         <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.94</v>
+        <v>-0.45</v>
       </c>
       <c r="H2" t="n">
         <v>0.25</v>
@@ -22695,7 +22695,7 @@
         <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="H2" t="n">
         <v>1.6</v>
@@ -33744,31 +33744,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.87</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.64</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.94</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="9">
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty Midcap 50</t>
+          <t>Nifty 50, Nifty Midcap 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.55%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>16326.2998046875</v>
       </c>
       <c r="G2" t="n">
-        <v>57843.94921875</v>
+        <v>57513.30078125</v>
       </c>
       <c r="H2" t="n">
         <v>21177.599609375</v>
@@ -11634,7 +11634,7 @@
         <v>0.52</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.45</v>
+        <v>-1.02</v>
       </c>
       <c r="H2" t="n">
         <v>-0.32</v>
@@ -22765,7 +22765,7 @@
         <v>-0.77</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="H2" t="n">
         <v>-0.58</v>
@@ -33853,7 +33853,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.45</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="7">
@@ -39499,7 +39499,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-1.3%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17014.599609375</v>
       </c>
       <c r="G2" t="n">
-        <v>59146.75</v>
+        <v>59898.19921875</v>
       </c>
       <c r="H2" t="n">
         <v>22045.19921875</v>
@@ -11739,7 +11739,7 @@
         <v>4.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>3.08</v>
       </c>
       <c r="H2" t="n">
         <v>3.76</v>
@@ -22975,7 +22975,7 @@
         <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="H2" t="n">
         <v>1.22</v>
@@ -34144,31 +34144,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty 50</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.57</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 50</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="7">
@@ -34260,12 +34260,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -39865,7 +39865,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>16741.75</v>
       </c>
       <c r="G2" t="n">
-        <v>59952.80078125</v>
+        <v>59374.80078125</v>
       </c>
       <c r="H2" t="n">
         <v>21875.94921875</v>
@@ -11914,7 +11914,7 @@
         <v>3.08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.17</v>
+        <v>2.18</v>
       </c>
       <c r="H2" t="n">
         <v>2.96</v>
@@ -23325,7 +23325,7 @@
         <v>-1.15</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="H2" t="n">
         <v>-1.01</v>
@@ -34649,31 +34649,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
@@ -34785,7 +34785,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -40475,7 +40475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>16882.5</v>
       </c>
       <c r="G2" t="n">
-        <v>60376.8984375</v>
+        <v>59784.8515625</v>
       </c>
       <c r="H2" t="n">
         <v>22000.05078125</v>
@@ -12054,7 +12054,7 @@
         <v>3.94</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>2.89</v>
       </c>
       <c r="H2" t="n">
         <v>3.55</v>
@@ -23605,7 +23605,7 @@
         <v>-0.86</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="H2" t="n">
         <v>-0.96</v>
@@ -35079,21 +35079,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.55</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="5">
@@ -35205,12 +35205,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty500 Multicap 50:25:25, Nifty 50</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty 200</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -40963,7 +40963,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17628.19921875</v>
       </c>
       <c r="G2" t="n">
-        <v>62003.1484375</v>
+        <v>61910.8984375</v>
       </c>
       <c r="H2" t="n">
         <v>22772.400390625</v>
@@ -12229,7 +12229,7 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>6.7</v>
+        <v>6.54</v>
       </c>
       <c r="H2" t="n">
         <v>7.18</v>
@@ -23955,7 +23955,7 @@
         <v>0.06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="H2" t="n">
         <v>-0.14</v>
@@ -35618,7 +35618,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="5">
@@ -35730,7 +35730,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -41573,7 +41573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17273.150390625</v>
       </c>
       <c r="G2" t="n">
-        <v>60839.69921875</v>
+        <v>60567.1484375</v>
       </c>
       <c r="H2" t="n">
         <v>22257.94921875</v>
@@ -12404,7 +12404,7 @@
         <v>6.35</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7</v>
+        <v>4.23</v>
       </c>
       <c r="H2" t="n">
         <v>4.76</v>
@@ -24305,7 +24305,7 @@
         <v>-0.49</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="H2" t="n">
         <v>-0.44</v>
@@ -36143,7 +36143,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="5">
@@ -36255,12 +36255,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -42183,7 +42183,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17478.25</v>
       </c>
       <c r="G2" t="n">
-        <v>61300.6015625</v>
+        <v>61389.30078125</v>
       </c>
       <c r="H2" t="n">
         <v>22504.19921875</v>
@@ -12579,7 +12579,7 @@
         <v>7.61</v>
       </c>
       <c r="G2" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="H2" t="n">
         <v>5.92</v>
@@ -24655,7 +24655,7 @@
         <v>0.14</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H2" t="n">
         <v>0.11</v>
@@ -36668,7 +36668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="5">
@@ -36785,7 +36785,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -42793,7 +42793,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17490.55078125</v>
       </c>
       <c r="G2" t="n">
-        <v>62558.8515625</v>
+        <v>61723.80078125</v>
       </c>
       <c r="H2" t="n">
         <v>22571.400390625</v>
@@ -12824,7 +12824,7 @@
         <v>7.69</v>
       </c>
       <c r="G2" t="n">
-        <v>7.66</v>
+        <v>6.22</v>
       </c>
       <c r="H2" t="n">
         <v>6.24</v>
@@ -25145,7 +25145,7 @@
         <v>-1.49</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="H2" t="n">
         <v>-1.37</v>
@@ -37389,21 +37389,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.66</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="5">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -43647,7 +43647,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17198.900390625</v>
       </c>
       <c r="G2" t="n">
-        <v>60966.6484375</v>
+        <v>60754.8984375</v>
       </c>
       <c r="H2" t="n">
         <v>22251.80078125</v>
@@ -12999,7 +12999,7 @@
         <v>5.89</v>
       </c>
       <c r="G2" t="n">
-        <v>4.92</v>
+        <v>4.55</v>
       </c>
       <c r="H2" t="n">
         <v>4.73</v>
@@ -25495,7 +25495,7 @@
         <v>-0.38</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="H2" t="n">
         <v>-0.29</v>
@@ -37914,21 +37914,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.92</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.73</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="5">
@@ -38040,12 +38040,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty 50</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -44257,7 +44257,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -503,7 +503,7 @@
         <v>17265.900390625</v>
       </c>
       <c r="G2" t="n">
-        <v>59325.3984375</v>
+        <v>60768.1015625</v>
       </c>
       <c r="H2" t="n">
         <v>22257.900390625</v>
@@ -13174,7 +13174,7 @@
         <v>6.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.09</v>
+        <v>4.58</v>
       </c>
       <c r="H2" t="n">
         <v>4.76</v>
@@ -25845,7 +25845,7 @@
         <v>2.37</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -38453,7 +38453,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.09</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="5">
@@ -38565,12 +38565,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Next 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24013.099609375</v>
       </c>
       <c r="C2" t="n">
-        <v>72356.6484375</v>
+        <v>70007.203125</v>
       </c>
       <c r="D2" t="n">
         <v>25086.650390625</v>
@@ -13337,7 +13337,7 @@
         <v>1.14</v>
       </c>
       <c r="C2" t="n">
-        <v>4.71</v>
+        <v>1.31</v>
       </c>
       <c r="D2" t="n">
         <v>0.23</v>
@@ -26183,7 +26183,7 @@
         <v>-0.64</v>
       </c>
       <c r="C2" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>-0.58</v>
@@ -38974,41 +38974,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.71</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.58</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.84</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.33</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
@@ -39024,11 +39024,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="10">
@@ -39090,7 +39090,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -45477,7 +45477,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24013.099609375</v>
       </c>
       <c r="C2" t="n">
-        <v>70007.203125</v>
+        <v>72356.6484375</v>
       </c>
       <c r="D2" t="n">
         <v>25086.650390625</v>
@@ -503,7 +503,7 @@
         <v>17735.30078125</v>
       </c>
       <c r="G2" t="n">
-        <v>60768.1015625</v>
+        <v>62517.30078125</v>
       </c>
       <c r="H2" t="n">
         <v>22972.94921875</v>
@@ -526,7 +526,7 @@
         <v>24168</v>
       </c>
       <c r="C3" t="n">
-        <v>70007.203125</v>
+        <v>72595.953125</v>
       </c>
       <c r="D3" t="n">
         <v>25233.650390625</v>
@@ -538,7 +538,7 @@
         <v>17716.849609375</v>
       </c>
       <c r="G3" t="n">
-        <v>60768.1015625</v>
+        <v>62379.25</v>
       </c>
       <c r="H3" t="n">
         <v>22893.19921875</v>
@@ -561,7 +561,7 @@
         <v>24085.69921875</v>
       </c>
       <c r="C4" t="n">
-        <v>70007.203125</v>
+        <v>72258.5</v>
       </c>
       <c r="D4" t="n">
         <v>25141.80078125</v>
@@ -573,7 +573,7 @@
         <v>17659.650390625</v>
       </c>
       <c r="G4" t="n">
-        <v>60768.1015625</v>
+        <v>62123.3515625</v>
       </c>
       <c r="H4" t="n">
         <v>22786.25</v>
@@ -596,7 +596,7 @@
         <v>23989.150390625</v>
       </c>
       <c r="C5" t="n">
-        <v>70007.203125</v>
+        <v>71798.6484375</v>
       </c>
       <c r="D5" t="n">
         <v>25029.900390625</v>
@@ -608,7 +608,7 @@
         <v>17607.150390625</v>
       </c>
       <c r="G5" t="n">
-        <v>60768.1015625</v>
+        <v>61802.05078125</v>
       </c>
       <c r="H5" t="n">
         <v>22671.400390625</v>
@@ -631,7 +631,7 @@
         <v>23853.900390625</v>
       </c>
       <c r="C6" t="n">
-        <v>70007.203125</v>
+        <v>71685.25</v>
       </c>
       <c r="D6" t="n">
         <v>24907.849609375</v>
@@ -643,7 +643,7 @@
         <v>17501.900390625</v>
       </c>
       <c r="G6" t="n">
-        <v>60768.1015625</v>
+        <v>61549.6484375</v>
       </c>
       <c r="H6" t="n">
         <v>22585.099609375</v>
@@ -13337,7 +13337,7 @@
         <v>1.14</v>
       </c>
       <c r="C2" t="n">
-        <v>1.31</v>
+        <v>4.71</v>
       </c>
       <c r="D2" t="n">
         <v>0.23</v>
@@ -13349,7 +13349,7 @@
         <v>9.19</v>
       </c>
       <c r="G2" t="n">
-        <v>4.58</v>
+        <v>7.59</v>
       </c>
       <c r="H2" t="n">
         <v>8.130000000000001</v>
@@ -13372,7 +13372,7 @@
         <v>1.79</v>
       </c>
       <c r="C3" t="n">
-        <v>1.31</v>
+        <v>5.05</v>
       </c>
       <c r="D3" t="n">
         <v>0.82</v>
@@ -13384,7 +13384,7 @@
         <v>9.08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.58</v>
+        <v>7.35</v>
       </c>
       <c r="H3" t="n">
         <v>7.75</v>
@@ -13407,7 +13407,7 @@
         <v>1.44</v>
       </c>
       <c r="C4" t="n">
-        <v>1.31</v>
+        <v>4.57</v>
       </c>
       <c r="D4" t="n">
         <v>0.45</v>
@@ -13419,7 +13419,7 @@
         <v>8.73</v>
       </c>
       <c r="G4" t="n">
-        <v>4.58</v>
+        <v>6.91</v>
       </c>
       <c r="H4" t="n">
         <v>7.25</v>
@@ -13442,7 +13442,7 @@
         <v>1.04</v>
       </c>
       <c r="C5" t="n">
-        <v>1.31</v>
+        <v>3.9</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -13454,7 +13454,7 @@
         <v>8.41</v>
       </c>
       <c r="G5" t="n">
-        <v>4.58</v>
+        <v>6.36</v>
       </c>
       <c r="H5" t="n">
         <v>6.71</v>
@@ -13477,7 +13477,7 @@
         <v>0.47</v>
       </c>
       <c r="C6" t="n">
-        <v>1.31</v>
+        <v>3.74</v>
       </c>
       <c r="D6" t="n">
         <v>-0.48</v>
@@ -13489,7 +13489,7 @@
         <v>7.76</v>
       </c>
       <c r="G6" t="n">
-        <v>4.58</v>
+        <v>5.92</v>
       </c>
       <c r="H6" t="n">
         <v>6.3</v>
@@ -26183,7 +26183,7 @@
         <v>-0.64</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="D2" t="n">
         <v>-0.58</v>
@@ -26195,7 +26195,7 @@
         <v>0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -26218,7 +26218,7 @@
         <v>0.34</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="D3" t="n">
         <v>0.37</v>
@@ -26230,7 +26230,7 @@
         <v>0.32</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="H3" t="n">
         <v>0.47</v>
@@ -26253,7 +26253,7 @@
         <v>0.4</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="D4" t="n">
         <v>0.45</v>
@@ -26265,7 +26265,7 @@
         <v>0.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="H4" t="n">
         <v>0.51</v>
@@ -26288,7 +26288,7 @@
         <v>0.57</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D5" t="n">
         <v>0.49</v>
@@ -26300,7 +26300,7 @@
         <v>0.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="n">
         <v>0.38</v>
@@ -26323,7 +26323,7 @@
         <v>0.98</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="D6" t="n">
         <v>1.24</v>
@@ -26335,7 +26335,7 @@
         <v>1.37</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="H6" t="n">
         <v>1.47</v>
@@ -38978,37 +38978,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.58</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.84</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.33</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.42</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8">
@@ -39024,11 +39024,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="10">
@@ -39090,7 +39090,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -39107,12 +39107,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -39124,12 +39124,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 150, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -39146,7 +39146,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -39158,12 +39158,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -45477,7 +45477,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24056</v>
       </c>
       <c r="C2" t="n">
-        <v>72356.6484375</v>
+        <v>72199.546875</v>
       </c>
       <c r="D2" t="n">
         <v>25114.099609375</v>
@@ -503,7 +503,7 @@
         <v>17587.849609375</v>
       </c>
       <c r="G2" t="n">
-        <v>62517.30078125</v>
+        <v>61795.5</v>
       </c>
       <c r="H2" t="n">
         <v>22751.05078125</v>
@@ -526,7 +526,7 @@
         <v>24056</v>
       </c>
       <c r="C3" t="n">
-        <v>72356.6484375</v>
+        <v>72199.546875</v>
       </c>
       <c r="D3" t="n">
         <v>25114.099609375</v>
@@ -538,7 +538,7 @@
         <v>17587.849609375</v>
       </c>
       <c r="G3" t="n">
-        <v>62517.30078125</v>
+        <v>61795.5</v>
       </c>
       <c r="H3" t="n">
         <v>22751.05078125</v>
@@ -561,7 +561,7 @@
         <v>24021.650390625</v>
       </c>
       <c r="C4" t="n">
-        <v>72356.6484375</v>
+        <v>72060.5</v>
       </c>
       <c r="D4" t="n">
         <v>25075.94921875</v>
@@ -573,7 +573,7 @@
         <v>17690.30078125</v>
       </c>
       <c r="G4" t="n">
-        <v>62517.30078125</v>
+        <v>62135.25</v>
       </c>
       <c r="H4" t="n">
         <v>22872.5</v>
@@ -596,7 +596,7 @@
         <v>23824.099609375</v>
       </c>
       <c r="C5" t="n">
-        <v>72356.6484375</v>
+        <v>72068.75</v>
       </c>
       <c r="D5" t="n">
         <v>24907.80078125</v>
@@ -608,7 +608,7 @@
         <v>17639.80078125</v>
       </c>
       <c r="G5" t="n">
-        <v>62517.30078125</v>
+        <v>62070.3515625</v>
       </c>
       <c r="H5" t="n">
         <v>22853.55078125</v>
@@ -631,7 +631,7 @@
         <v>24102.900390625</v>
       </c>
       <c r="C6" t="n">
-        <v>72356.6484375</v>
+        <v>73073.203125</v>
       </c>
       <c r="D6" t="n">
         <v>25209.55078125</v>
@@ -643,7 +643,7 @@
         <v>17800.44921875</v>
       </c>
       <c r="G6" t="n">
-        <v>62517.30078125</v>
+        <v>62729.1015625</v>
       </c>
       <c r="H6" t="n">
         <v>23073.05078125</v>
@@ -13512,7 +13512,7 @@
         <v>1.32</v>
       </c>
       <c r="C2" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
       <c r="D2" t="n">
         <v>0.34</v>
@@ -13524,7 +13524,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>7.59</v>
+        <v>6.35</v>
       </c>
       <c r="H2" t="n">
         <v>7.08</v>
@@ -13547,7 +13547,7 @@
         <v>1.32</v>
       </c>
       <c r="C3" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
       <c r="D3" t="n">
         <v>0.34</v>
@@ -13559,7 +13559,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>7.59</v>
+        <v>6.35</v>
       </c>
       <c r="H3" t="n">
         <v>7.08</v>
@@ -13582,7 +13582,7 @@
         <v>1.17</v>
       </c>
       <c r="C4" t="n">
-        <v>4.71</v>
+        <v>4.28</v>
       </c>
       <c r="D4" t="n">
         <v>0.19</v>
@@ -13594,7 +13594,7 @@
         <v>8.92</v>
       </c>
       <c r="G4" t="n">
-        <v>7.59</v>
+        <v>6.93</v>
       </c>
       <c r="H4" t="n">
         <v>7.65</v>
@@ -13617,7 +13617,7 @@
         <v>0.34</v>
       </c>
       <c r="C5" t="n">
-        <v>4.71</v>
+        <v>4.29</v>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
@@ -13629,7 +13629,7 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>7.59</v>
+        <v>6.82</v>
       </c>
       <c r="H5" t="n">
         <v>7.56</v>
@@ -13652,7 +13652,7 @@
         <v>1.52</v>
       </c>
       <c r="C6" t="n">
-        <v>4.71</v>
+        <v>5.74</v>
       </c>
       <c r="D6" t="n">
         <v>0.72</v>
@@ -13664,7 +13664,7 @@
         <v>9.6</v>
       </c>
       <c r="G6" t="n">
-        <v>7.59</v>
+        <v>7.95</v>
       </c>
       <c r="H6" t="n">
         <v>8.6</v>
@@ -26568,7 +26568,7 @@
         <v>0.14</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="D3" t="n">
         <v>0.15</v>
@@ -26580,7 +26580,7 @@
         <v>-0.58</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="H3" t="n">
         <v>-0.53</v>
@@ -26603,7 +26603,7 @@
         <v>0.83</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D4" t="n">
         <v>0.68</v>
@@ -26615,7 +26615,7 @@
         <v>0.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
         <v>0.08</v>
@@ -26638,7 +26638,7 @@
         <v>-1.16</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
       <c r="D5" t="n">
         <v>-1.2</v>
@@ -26650,7 +26650,7 @@
         <v>-0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="H5" t="n">
         <v>-0.95</v>
@@ -26673,7 +26673,7 @@
         <v>0.37</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="D6" t="n">
         <v>0.49</v>
@@ -26685,7 +26685,7 @@
         <v>0.37</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
         <v>0.44</v>
@@ -39489,21 +39489,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.59</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.08</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="5">
@@ -39513,7 +39513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="6">
@@ -39632,12 +39632,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty 100, Nifty 50, Nifty 200</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -39666,12 +39666,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nifty 100, Nifty 200, Nifty 50</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -39683,12 +39683,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted, Nifty 500</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty Midcap 100, Nifty 50, Nifty Midcap 50</t>
         </is>
       </c>
     </row>
@@ -46087,7 +46087,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24270.849609375</v>
       </c>
       <c r="C2" t="n">
-        <v>72268.953125</v>
+        <v>72199.546875</v>
       </c>
       <c r="D2" t="n">
         <v>25301.900390625</v>
@@ -13687,7 +13687,7 @@
         <v>2.22</v>
       </c>
       <c r="C2" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
       <c r="D2" t="n">
         <v>1.09</v>
@@ -26883,7 +26883,7 @@
         <v>0.39</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0.28</v>
@@ -40048,7 +40048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="7">

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24270.849609375</v>
       </c>
       <c r="C2" t="n">
-        <v>72199.546875</v>
+        <v>72268.953125</v>
       </c>
       <c r="D2" t="n">
         <v>25301.900390625</v>
@@ -503,7 +503,7 @@
         <v>17783.25</v>
       </c>
       <c r="G2" t="n">
-        <v>61795.5</v>
+        <v>62190.30078125</v>
       </c>
       <c r="H2" t="n">
         <v>22884.349609375</v>
@@ -526,7 +526,7 @@
         <v>24175.69921875</v>
       </c>
       <c r="C3" t="n">
-        <v>72199.546875</v>
+        <v>72418.546875</v>
       </c>
       <c r="D3" t="n">
         <v>25230.19921875</v>
@@ -538,7 +538,7 @@
         <v>17806</v>
       </c>
       <c r="G3" t="n">
-        <v>61795.5</v>
+        <v>62307.8984375</v>
       </c>
       <c r="H3" t="n">
         <v>22934.900390625</v>
@@ -561,7 +561,7 @@
         <v>24005.849609375</v>
       </c>
       <c r="C4" t="n">
-        <v>72199.546875</v>
+        <v>72100.6484375</v>
       </c>
       <c r="D4" t="n">
         <v>25065.099609375</v>
@@ -573,7 +573,7 @@
         <v>17716.099609375</v>
       </c>
       <c r="G4" t="n">
-        <v>61795.5</v>
+        <v>62008.80078125</v>
       </c>
       <c r="H4" t="n">
         <v>22823.5</v>
@@ -596,7 +596,7 @@
         <v>23865.75</v>
       </c>
       <c r="C5" t="n">
-        <v>72199.546875</v>
+        <v>71629.453125</v>
       </c>
       <c r="D5" t="n">
         <v>24915.599609375</v>
@@ -608,7 +608,7 @@
         <v>17594.900390625</v>
       </c>
       <c r="G5" t="n">
-        <v>61795.5</v>
+        <v>61797.69921875</v>
       </c>
       <c r="H5" t="n">
         <v>22774.25</v>
@@ -631,7 +631,7 @@
         <v>23946.25</v>
       </c>
       <c r="C6" t="n">
-        <v>72199.546875</v>
+        <v>71510.296875</v>
       </c>
       <c r="D6" t="n">
         <v>24976.69921875</v>
@@ -643,7 +643,7 @@
         <v>17521</v>
       </c>
       <c r="G6" t="n">
-        <v>61795.5</v>
+        <v>61567.30078125</v>
       </c>
       <c r="H6" t="n">
         <v>22679.650390625</v>
@@ -13687,7 +13687,7 @@
         <v>2.22</v>
       </c>
       <c r="C2" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
       <c r="D2" t="n">
         <v>1.09</v>
@@ -13699,7 +13699,7 @@
         <v>9.49</v>
       </c>
       <c r="G2" t="n">
-        <v>6.35</v>
+        <v>7.03</v>
       </c>
       <c r="H2" t="n">
         <v>7.71</v>
@@ -13722,7 +13722,7 @@
         <v>1.82</v>
       </c>
       <c r="C3" t="n">
-        <v>4.48</v>
+        <v>4.8</v>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
@@ -13734,7 +13734,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>6.35</v>
+        <v>7.23</v>
       </c>
       <c r="H3" t="n">
         <v>7.95</v>
@@ -13757,7 +13757,7 @@
         <v>1.11</v>
       </c>
       <c r="C4" t="n">
-        <v>4.48</v>
+        <v>4.34</v>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
@@ -13769,7 +13769,7 @@
         <v>9.08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.35</v>
+        <v>6.71</v>
       </c>
       <c r="H4" t="n">
         <v>7.42</v>
@@ -13792,7 +13792,7 @@
         <v>0.52</v>
       </c>
       <c r="C5" t="n">
-        <v>4.48</v>
+        <v>3.66</v>
       </c>
       <c r="D5" t="n">
         <v>-0.45</v>
@@ -13827,7 +13827,7 @@
         <v>0.86</v>
       </c>
       <c r="C6" t="n">
-        <v>4.48</v>
+        <v>3.48</v>
       </c>
       <c r="D6" t="n">
         <v>-0.21</v>
@@ -13839,7 +13839,7 @@
         <v>7.87</v>
       </c>
       <c r="G6" t="n">
-        <v>6.35</v>
+        <v>5.95</v>
       </c>
       <c r="H6" t="n">
         <v>6.75</v>
@@ -26883,7 +26883,7 @@
         <v>0.39</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="D2" t="n">
         <v>0.28</v>
@@ -26895,7 +26895,7 @@
         <v>-0.13</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="H2" t="n">
         <v>-0.22</v>
@@ -26918,7 +26918,7 @@
         <v>0.71</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="D3" t="n">
         <v>0.66</v>
@@ -26930,7 +26930,7 @@
         <v>0.51</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="H3" t="n">
         <v>0.49</v>
@@ -26953,7 +26953,7 @@
         <v>0.59</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="D4" t="n">
         <v>0.6</v>
@@ -26965,7 +26965,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="H4" t="n">
         <v>0.22</v>
@@ -26988,7 +26988,7 @@
         <v>-0.34</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="D5" t="n">
         <v>-0.24</v>
@@ -27000,7 +27000,7 @@
         <v>0.42</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -27023,7 +27023,7 @@
         <v>-0.46</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="D6" t="n">
         <v>-0.55</v>
@@ -27035,7 +27035,7 @@
         <v>-0.38</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="H6" t="n">
         <v>-0.31</v>
@@ -40028,7 +40028,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.35</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="5">
@@ -40048,7 +40048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="7">
@@ -40145,7 +40145,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -40174,12 +40174,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty 100, Nifty 50</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty 100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -40191,7 +40191,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -40208,12 +40208,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nifty 100, Nifty500 Multicap 50:25:25, Nifty 200</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.49%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24206.900390625</v>
       </c>
       <c r="C2" t="n">
-        <v>72391.796875</v>
+        <v>72268.953125</v>
       </c>
       <c r="D2" t="n">
         <v>25255.099609375</v>
@@ -13862,7 +13862,7 @@
         <v>1.95</v>
       </c>
       <c r="C2" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="D2" t="n">
         <v>0.9</v>
@@ -27233,7 +27233,7 @@
         <v>1.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>1.06</v>
@@ -40573,7 +40573,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="7">
@@ -40670,7 +40670,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty 50</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
         </is>
       </c>
     </row>
@@ -47307,7 +47307,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.86%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24206.900390625</v>
       </c>
       <c r="C2" t="n">
-        <v>72268.953125</v>
+        <v>72391.796875</v>
       </c>
       <c r="D2" t="n">
         <v>25255.099609375</v>
@@ -503,7 +503,7 @@
         <v>18059.5</v>
       </c>
       <c r="G2" t="n">
-        <v>62190.30078125</v>
+        <v>63036.80078125</v>
       </c>
       <c r="H2" t="n">
         <v>23166.5</v>
@@ -526,7 +526,7 @@
         <v>23962.80078125</v>
       </c>
       <c r="C3" t="n">
-        <v>72268.953125</v>
+        <v>71485.8515625</v>
       </c>
       <c r="D3" t="n">
         <v>24989.25</v>
@@ -538,7 +538,7 @@
         <v>17844.5</v>
       </c>
       <c r="G3" t="n">
-        <v>62190.30078125</v>
+        <v>62166.8515625</v>
       </c>
       <c r="H3" t="n">
         <v>22855.75</v>
@@ -561,7 +561,7 @@
         <v>23882.05078125</v>
       </c>
       <c r="C4" t="n">
-        <v>72268.953125</v>
+        <v>70898.75</v>
       </c>
       <c r="D4" t="n">
         <v>24883.05078125</v>
@@ -573,7 +573,7 @@
         <v>17604.44921875</v>
       </c>
       <c r="G4" t="n">
-        <v>62190.30078125</v>
+        <v>61322.75</v>
       </c>
       <c r="H4" t="n">
         <v>22537.849609375</v>
@@ -596,7 +596,7 @@
         <v>24398.69921875</v>
       </c>
       <c r="C5" t="n">
-        <v>72268.953125</v>
+        <v>72248.453125</v>
       </c>
       <c r="D5" t="n">
         <v>25409.650390625</v>
@@ -608,7 +608,7 @@
         <v>17864.05078125</v>
       </c>
       <c r="G5" t="n">
-        <v>62190.30078125</v>
+        <v>62285.30078125</v>
       </c>
       <c r="H5" t="n">
         <v>22912.30078125</v>
@@ -631,7 +631,7 @@
         <v>24430.349609375</v>
       </c>
       <c r="C6" t="n">
-        <v>72268.953125</v>
+        <v>72685.6015625</v>
       </c>
       <c r="D6" t="n">
         <v>25464.44921875</v>
@@ -643,7 +643,7 @@
         <v>17863.55078125</v>
       </c>
       <c r="G6" t="n">
-        <v>62190.30078125</v>
+        <v>62471.5</v>
       </c>
       <c r="H6" t="n">
         <v>22973.349609375</v>
@@ -13862,7 +13862,7 @@
         <v>1.95</v>
       </c>
       <c r="C2" t="n">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
       <c r="D2" t="n">
         <v>0.9</v>
@@ -13874,7 +13874,7 @@
         <v>11.19</v>
       </c>
       <c r="G2" t="n">
-        <v>7.03</v>
+        <v>8.48</v>
       </c>
       <c r="H2" t="n">
         <v>9.039999999999999</v>
@@ -13897,7 +13897,7 @@
         <v>0.93</v>
       </c>
       <c r="C3" t="n">
-        <v>4.58</v>
+        <v>3.45</v>
       </c>
       <c r="D3" t="n">
         <v>-0.16</v>
@@ -13909,7 +13909,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>7.03</v>
+        <v>6.98</v>
       </c>
       <c r="H3" t="n">
         <v>7.57</v>
@@ -13932,7 +13932,7 @@
         <v>0.59</v>
       </c>
       <c r="C4" t="n">
-        <v>4.58</v>
+        <v>2.6</v>
       </c>
       <c r="D4" t="n">
         <v>-0.58</v>
@@ -13944,7 +13944,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>7.03</v>
+        <v>5.53</v>
       </c>
       <c r="H4" t="n">
         <v>6.08</v>
@@ -13967,7 +13967,7 @@
         <v>2.76</v>
       </c>
       <c r="C5" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="D5" t="n">
         <v>1.52</v>
@@ -13979,7 +13979,7 @@
         <v>9.99</v>
       </c>
       <c r="G5" t="n">
-        <v>7.03</v>
+        <v>7.19</v>
       </c>
       <c r="H5" t="n">
         <v>7.84</v>
@@ -14002,7 +14002,7 @@
         <v>2.9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.58</v>
+        <v>5.18</v>
       </c>
       <c r="D6" t="n">
         <v>1.74</v>
@@ -14014,7 +14014,7 @@
         <v>9.98</v>
       </c>
       <c r="G6" t="n">
-        <v>7.03</v>
+        <v>7.51</v>
       </c>
       <c r="H6" t="n">
         <v>8.130000000000001</v>
@@ -27233,7 +27233,7 @@
         <v>1.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="D2" t="n">
         <v>1.06</v>
@@ -27245,7 +27245,7 @@
         <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H2" t="n">
         <v>1.36</v>
@@ -27268,7 +27268,7 @@
         <v>0.34</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="D3" t="n">
         <v>0.43</v>
@@ -27280,7 +27280,7 @@
         <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="H3" t="n">
         <v>1.41</v>
@@ -27303,7 +27303,7 @@
         <v>-2.12</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="D4" t="n">
         <v>-2.07</v>
@@ -27315,7 +27315,7 @@
         <v>-1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-1.55</v>
       </c>
       <c r="H4" t="n">
         <v>-1.63</v>
@@ -27338,7 +27338,7 @@
         <v>-0.13</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="D5" t="n">
         <v>-0.22</v>
@@ -27350,7 +27350,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H5" t="n">
         <v>-0.27</v>
@@ -27373,7 +27373,7 @@
         <v>0.66</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="D6" t="n">
         <v>0.64</v>
@@ -27385,7 +27385,7 @@
         <v>0.45</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H6" t="n">
         <v>0.39</v>
@@ -40553,7 +40553,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.03</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="5">
@@ -40573,7 +40573,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7">
@@ -40665,12 +40665,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Midcap 50</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -40682,12 +40682,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -40699,7 +40699,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -40716,12 +40716,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 100</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty 100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted, Nifty 500</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -40738,7 +40738,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -47307,7 +47307,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24334.30078125</v>
       </c>
       <c r="C2" t="n">
-        <v>71828.3984375</v>
+        <v>72391.796875</v>
       </c>
       <c r="D2" t="n">
         <v>25327.650390625</v>
@@ -14037,7 +14037,7 @@
         <v>2.49</v>
       </c>
       <c r="C2" t="n">
-        <v>3.94</v>
+        <v>4.76</v>
       </c>
       <c r="D2" t="n">
         <v>1.19</v>
@@ -27583,7 +27583,7 @@
         <v>1.09</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0.87</v>
@@ -41094,21 +41094,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="8">
@@ -41195,7 +41195,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
         </is>
       </c>
     </row>
@@ -47917,7 +47917,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -491,7 +491,7 @@
         <v>24334.30078125</v>
       </c>
       <c r="C2" t="n">
-        <v>72391.796875</v>
+        <v>71828.3984375</v>
       </c>
       <c r="D2" t="n">
         <v>25327.650390625</v>
@@ -503,7 +503,7 @@
         <v>17930.849609375</v>
       </c>
       <c r="G2" t="n">
-        <v>63036.80078125</v>
+        <v>62428.05078125</v>
       </c>
       <c r="H2" t="n">
         <v>22967.900390625</v>
@@ -526,7 +526,7 @@
         <v>24072.75</v>
       </c>
       <c r="C3" t="n">
-        <v>72391.796875</v>
+        <v>71896.75</v>
       </c>
       <c r="D3" t="n">
         <v>25109.19921875</v>
@@ -538,7 +538,7 @@
         <v>17985.099609375</v>
       </c>
       <c r="G3" t="n">
-        <v>63036.80078125</v>
+        <v>62686.75</v>
       </c>
       <c r="H3" t="n">
         <v>23060.05078125</v>
@@ -561,7 +561,7 @@
         <v>24078.5</v>
       </c>
       <c r="C4" t="n">
-        <v>72391.796875</v>
+        <v>72148.796875</v>
       </c>
       <c r="D4" t="n">
         <v>25130.099609375</v>
@@ -573,7 +573,7 @@
         <v>18036.75</v>
       </c>
       <c r="G4" t="n">
-        <v>63036.80078125</v>
+        <v>62943.19921875</v>
       </c>
       <c r="H4" t="n">
         <v>23153.400390625</v>
@@ -596,7 +596,7 @@
         <v>24052.05078125</v>
       </c>
       <c r="C5" t="n">
-        <v>72391.796875</v>
+        <v>71851.6015625</v>
       </c>
       <c r="D5" t="n">
         <v>25088.650390625</v>
@@ -608,7 +608,7 @@
         <v>17988.150390625</v>
       </c>
       <c r="G5" t="n">
-        <v>63036.80078125</v>
+        <v>62766.3984375</v>
       </c>
       <c r="H5" t="n">
         <v>23053.599609375</v>
@@ -631,7 +631,7 @@
         <v>24211</v>
       </c>
       <c r="C6" t="n">
-        <v>72391.796875</v>
+        <v>72111.3984375</v>
       </c>
       <c r="D6" t="n">
         <v>25240.80078125</v>
@@ -643,7 +643,7 @@
         <v>18089.55078125</v>
       </c>
       <c r="G6" t="n">
-        <v>63036.80078125</v>
+        <v>63040.94921875</v>
       </c>
       <c r="H6" t="n">
         <v>23167.400390625</v>
@@ -14037,7 +14037,7 @@
         <v>2.49</v>
       </c>
       <c r="C2" t="n">
-        <v>4.76</v>
+        <v>3.94</v>
       </c>
       <c r="D2" t="n">
         <v>1.19</v>
@@ -14049,7 +14049,7 @@
         <v>10.4</v>
       </c>
       <c r="G2" t="n">
-        <v>8.48</v>
+        <v>7.43</v>
       </c>
       <c r="H2" t="n">
         <v>8.1</v>
@@ -14072,7 +14072,7 @@
         <v>1.39</v>
       </c>
       <c r="C3" t="n">
-        <v>4.76</v>
+        <v>4.04</v>
       </c>
       <c r="D3" t="n">
         <v>0.32</v>
@@ -14084,7 +14084,7 @@
         <v>10.73</v>
       </c>
       <c r="G3" t="n">
-        <v>8.48</v>
+        <v>7.88</v>
       </c>
       <c r="H3" t="n">
         <v>8.539999999999999</v>
@@ -14107,7 +14107,7 @@
         <v>1.41</v>
       </c>
       <c r="C4" t="n">
-        <v>4.76</v>
+        <v>4.41</v>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
@@ -14119,7 +14119,7 @@
         <v>11.05</v>
       </c>
       <c r="G4" t="n">
-        <v>8.48</v>
+        <v>8.32</v>
       </c>
       <c r="H4" t="n">
         <v>8.98</v>
@@ -14142,7 +14142,7 @@
         <v>1.3</v>
       </c>
       <c r="C5" t="n">
-        <v>4.76</v>
+        <v>3.98</v>
       </c>
       <c r="D5" t="n">
         <v>0.24</v>
@@ -14154,7 +14154,7 @@
         <v>10.75</v>
       </c>
       <c r="G5" t="n">
-        <v>8.48</v>
+        <v>8.02</v>
       </c>
       <c r="H5" t="n">
         <v>8.51</v>
@@ -14177,7 +14177,7 @@
         <v>1.97</v>
       </c>
       <c r="C6" t="n">
-        <v>4.76</v>
+        <v>4.35</v>
       </c>
       <c r="D6" t="n">
         <v>0.85</v>
@@ -14189,7 +14189,7 @@
         <v>11.38</v>
       </c>
       <c r="G6" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="H6" t="n">
         <v>9.039999999999999</v>
@@ -27583,7 +27583,7 @@
         <v>1.09</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D2" t="n">
         <v>0.87</v>
@@ -27595,7 +27595,7 @@
         <v>-0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="H2" t="n">
         <v>-0.4</v>
@@ -27618,7 +27618,7 @@
         <v>-0.02</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
@@ -27630,7 +27630,7 @@
         <v>-0.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="H3" t="n">
         <v>-0.4</v>
@@ -27653,7 +27653,7 @@
         <v>0.11</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="D4" t="n">
         <v>0.17</v>
@@ -27665,7 +27665,7 @@
         <v>0.27</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
         <v>0.43</v>
@@ -27688,7 +27688,7 @@
         <v>-0.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="D5" t="n">
         <v>-0.6</v>
@@ -27700,7 +27700,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="H5" t="n">
         <v>-0.49</v>
@@ -27723,7 +27723,7 @@
         <v>0.02</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
@@ -27735,7 +27735,7 @@
         <v>0.17</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -41064,21 +41064,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.48</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.1</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="5">
@@ -41094,21 +41094,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.76</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="8">
@@ -41195,7 +41195,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Midcap 50</t>
         </is>
       </c>
     </row>
@@ -41207,12 +41207,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Next 50</t>
         </is>
       </c>
     </row>
@@ -41224,12 +41224,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -41258,12 +41258,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty 50, Nifty Next 50</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 100, Nifty 200</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -47917,7 +47917,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -488,34 +488,34 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>23767.44921875</v>
+        <v>23869.599609375</v>
       </c>
       <c r="C2" t="n">
-        <v>71766</v>
+        <v>71828.3984375</v>
       </c>
       <c r="D2" t="n">
-        <v>24840.75</v>
+        <v>24932.5</v>
       </c>
       <c r="E2" t="n">
-        <v>13762.400390625</v>
+        <v>13805.849609375</v>
       </c>
       <c r="F2" t="n">
-        <v>17709.44921875</v>
+        <v>17690.5</v>
       </c>
       <c r="G2" t="n">
         <v>62428.05078125</v>
       </c>
       <c r="H2" t="n">
-        <v>22685.25</v>
+        <v>22705.25</v>
       </c>
       <c r="I2" t="n">
-        <v>22913.30078125</v>
+        <v>22982.400390625</v>
       </c>
       <c r="J2" t="n">
         <v>16.3799991607666</v>
       </c>
       <c r="K2" t="n">
-        <v>22913.30078125</v>
+        <v>22982.400390625</v>
       </c>
     </row>
     <row r="3">
@@ -14209,34 +14209,34 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="C2" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.75</v>
+        <v>-0.38</v>
       </c>
       <c r="E2" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="F2" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="G2" t="n">
         <v>7.43</v>
       </c>
       <c r="H2" t="n">
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="I2" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="J2" t="n">
         <v>3.08</v>
       </c>
       <c r="K2" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="3">
@@ -27930,34 +27930,34 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.43</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>-0.3</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -41583,7 +41583,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="3">
@@ -41603,7 +41603,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="5">
@@ -41613,7 +41613,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="6">
@@ -41633,7 +41633,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="8">
@@ -41643,7 +41643,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="9">
@@ -41653,7 +41653,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="10">
@@ -41663,7 +41663,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="11">
@@ -41673,7 +41673,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.75</v>
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -41715,12 +41715,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Next 50</t>
+          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty Next 50</t>
         </is>
       </c>
     </row>
@@ -48527,7 +48527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -488,34 +488,34 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>23869.599609375</v>
+        <v>23767.44921875</v>
       </c>
       <c r="C2" t="n">
         <v>71828.3984375</v>
       </c>
       <c r="D2" t="n">
-        <v>24932.5</v>
+        <v>24840.75</v>
       </c>
       <c r="E2" t="n">
-        <v>13805.849609375</v>
+        <v>13762.400390625</v>
       </c>
       <c r="F2" t="n">
-        <v>17690.5</v>
+        <v>17709.44921875</v>
       </c>
       <c r="G2" t="n">
         <v>62428.05078125</v>
       </c>
       <c r="H2" t="n">
-        <v>22705.25</v>
+        <v>22685.25</v>
       </c>
       <c r="I2" t="n">
-        <v>22982.400390625</v>
+        <v>22913.30078125</v>
       </c>
       <c r="J2" t="n">
         <v>16.3799991607666</v>
       </c>
       <c r="K2" t="n">
-        <v>22982.400390625</v>
+        <v>22913.30078125</v>
       </c>
     </row>
     <row r="3">
@@ -14209,34 +14209,34 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
         <v>3.94</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="E2" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="F2" t="n">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>7.43</v>
       </c>
       <c r="H2" t="n">
-        <v>6.87</v>
+        <v>6.77</v>
       </c>
       <c r="I2" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
       <c r="J2" t="n">
         <v>3.08</v>
       </c>
       <c r="K2" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="3">
@@ -27930,34 +27930,34 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="J2" t="n">
         <v>-0.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3">
@@ -41583,7 +41583,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -41603,7 +41603,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.87</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="5">
@@ -41633,7 +41633,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="8">
@@ -41643,7 +41643,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -41653,7 +41653,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="10">
@@ -41663,7 +41663,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -41673,7 +41673,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.38</v>
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -41715,12 +41715,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty Next 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -48527,7 +48527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -512,7 +512,7 @@
         <v>23594.900390625</v>
       </c>
       <c r="J2" t="n">
-        <v>16.92000007629395</v>
+        <v>16.93000030517578</v>
       </c>
       <c r="K2" t="n">
         <v>23594.900390625</v>
@@ -547,7 +547,7 @@
         <v>23658.099609375</v>
       </c>
       <c r="J3" t="n">
-        <v>16.94000053405762</v>
+        <v>16.93000030517578</v>
       </c>
       <c r="K3" t="n">
         <v>23658.099609375</v>
@@ -14758,7 +14758,7 @@
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
@@ -14793,7 +14793,7 @@
         <v>3.67</v>
       </c>
       <c r="J3" t="n">
-        <v>6.61</v>
+        <v>6.54</v>
       </c>
       <c r="K3" t="n">
         <v>3.67</v>
@@ -29004,7 +29004,7 @@
         <v>-0.27</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>-0.27</v>
@@ -29039,7 +29039,7 @@
         <v>-0.06</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="K3" t="n">
         <v>-0.06</v>
@@ -43198,7 +43198,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="7">
@@ -43290,7 +43290,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 100, Nifty500 Multicap 50:25:25, Nifty 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -50357,7 +50357,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>6.24%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -485,37 +485,37 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="n">
-        <v>24287.650390625</v>
+        <v>24154.900390625</v>
       </c>
       <c r="C2" t="n">
-        <v>74474.1015625</v>
+        <v>74308.8984375</v>
       </c>
       <c r="D2" t="n">
-        <v>25457.30078125</v>
+        <v>25333.650390625</v>
       </c>
       <c r="E2" t="n">
-        <v>14133.849609375</v>
+        <v>14066.650390625</v>
       </c>
       <c r="F2" t="n">
-        <v>18279</v>
+        <v>18216.80078125</v>
       </c>
       <c r="G2" t="n">
         <v>62428.05078125</v>
       </c>
       <c r="H2" t="n">
-        <v>23454.94921875</v>
+        <v>23364.900390625</v>
       </c>
       <c r="I2" t="n">
-        <v>23564.44921875</v>
+        <v>23472.400390625</v>
       </c>
       <c r="J2" t="n">
-        <v>16.94000053405762</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="K2" t="n">
-        <v>23564.44921875</v>
+        <v>23472.400390625</v>
       </c>
     </row>
     <row r="3">
@@ -14766,37 +14766,37 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="C2" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="E2" t="n">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
       <c r="F2" t="n">
-        <v>12.54</v>
+        <v>12.16</v>
       </c>
       <c r="G2" t="n">
         <v>7.43</v>
       </c>
       <c r="H2" t="n">
-        <v>10.39</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
-        <v>6.61</v>
+        <v>6.67</v>
       </c>
       <c r="K2" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="3">
@@ -29047,37 +29047,37 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.32</v>
+        <v>-0.87</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.26</v>
+        <v>-0.75</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>-0.24</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.13</v>
+        <v>-0.52</v>
       </c>
       <c r="J2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.13</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="3">
@@ -43263,7 +43263,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.54</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="3">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.39</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -43283,7 +43283,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -43303,7 +43303,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.61</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="7">
@@ -43313,7 +43313,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="8">
@@ -43323,7 +43323,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="9">
@@ -43333,7 +43333,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="10">
@@ -43343,7 +43343,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="11">
@@ -43353,7 +43353,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
@@ -43390,12 +43390,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-Aug-26</t>
+          <t>18-Aug-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Midcap 50</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 100, Nifty Next 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -50479,7 +50479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>5.83%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>23530.30078125</v>
       </c>
       <c r="I2" t="n">
-        <v>16.88999938964844</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="J2" t="n">
         <v>23530.30078125</v>
@@ -13690,7 +13690,7 @@
         <v>3.11</v>
       </c>
       <c r="I2" t="n">
-        <v>6.29</v>
+        <v>6.36</v>
       </c>
       <c r="J2" t="n">
         <v>3.11</v>
@@ -26876,7 +26876,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J2" t="n">
         <v>0.07000000000000001</v>
@@ -40010,7 +40010,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.29</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="6">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -47241,7 +47241,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.82%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>23482</v>
       </c>
       <c r="I2" t="n">
-        <v>16.97999954223633</v>
+        <v>16.88999938964844</v>
       </c>
       <c r="J2" t="n">
         <v>23482</v>
@@ -536,7 +536,7 @@
         <v>23482</v>
       </c>
       <c r="I3" t="n">
-        <v>16.97999954223633</v>
+        <v>16.88999938964844</v>
       </c>
       <c r="J3" t="n">
         <v>23482</v>
@@ -13850,7 +13850,7 @@
         <v>2.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.86</v>
+        <v>6.29</v>
       </c>
       <c r="J2" t="n">
         <v>2.9</v>
@@ -13882,7 +13882,7 @@
         <v>2.9</v>
       </c>
       <c r="I3" t="n">
-        <v>6.86</v>
+        <v>6.29</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
@@ -27228,7 +27228,7 @@
         <v>-0.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="J3" t="n">
         <v>-0.33</v>
@@ -40490,7 +40490,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.86</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="6">
@@ -40599,12 +40599,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty Next 50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -47806,7 +47806,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.74%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -512,7 +512,7 @@
         <v>23254.150390625</v>
       </c>
       <c r="J2" t="n">
-        <v>16.79000091552734</v>
+        <v>16.75</v>
       </c>
       <c r="K2" t="n">
         <v>23254.150390625</v>
@@ -547,7 +547,7 @@
         <v>23254.05078125</v>
       </c>
       <c r="J3" t="n">
-        <v>16.68000030517578</v>
+        <v>16.75</v>
       </c>
       <c r="K3" t="n">
         <v>23254.05078125</v>
@@ -15283,7 +15283,7 @@
         <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>5.66</v>
+        <v>5.41</v>
       </c>
       <c r="K2" t="n">
         <v>1.9</v>
@@ -15318,7 +15318,7 @@
         <v>1.9</v>
       </c>
       <c r="J3" t="n">
-        <v>4.97</v>
+        <v>5.41</v>
       </c>
       <c r="K3" t="n">
         <v>1.9</v>
@@ -30054,7 +30054,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -30089,7 +30089,7 @@
         <v>0.13</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="K3" t="n">
         <v>0.13</v>
@@ -44773,7 +44773,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.66</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="7">
@@ -44865,7 +44865,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -44882,7 +44882,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -512,7 +512,7 @@
         <v>23254.150390625</v>
       </c>
       <c r="J2" t="n">
-        <v>16.75</v>
+        <v>16.79000091552734</v>
       </c>
       <c r="K2" t="n">
         <v>23254.150390625</v>
@@ -15283,7 +15283,7 @@
         <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
       <c r="K2" t="n">
         <v>1.9</v>
@@ -30054,7 +30054,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -44773,7 +44773,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="7">
@@ -44865,7 +44865,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty Midcap 100</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.83%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -512,7 +512,7 @@
         <v>22866.5</v>
       </c>
       <c r="J2" t="n">
-        <v>16.51000022888184</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="K2" t="n">
         <v>22866.5</v>
@@ -547,7 +547,7 @@
         <v>22952.349609375</v>
       </c>
       <c r="J3" t="n">
-        <v>16.60000038146973</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="K3" t="n">
         <v>22952.349609375</v>
@@ -15458,7 +15458,7 @@
         <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="K2" t="n">
         <v>0.2</v>
@@ -15493,7 +15493,7 @@
         <v>0.58</v>
       </c>
       <c r="J3" t="n">
-        <v>4.47</v>
+        <v>4.03</v>
       </c>
       <c r="K3" t="n">
         <v>0.58</v>
@@ -30404,7 +30404,7 @@
         <v>-0.37</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>-0.37</v>
@@ -30439,7 +30439,7 @@
         <v>-0.03</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="K3" t="n">
         <v>-0.03</v>
@@ -45298,7 +45298,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="7">
@@ -45390,12 +45390,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -45412,7 +45412,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -52797,7 +52797,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
